--- a/配置表格/G怪物刷新配置.xlsx
+++ b/配置表格/G怪物刷新配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22091" windowHeight="9144"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="spawn_config" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">spawn_config!$A$2:$Z$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">spawn_config!$A$4:$AB$217</definedName>
     <definedName name="怪物类型">[1]名称表!$A$3:$A$26</definedName>
     <definedName name="说明">[2]名称表!$A$3:$A$26</definedName>
     <definedName name="阵营">[1]名称表!$H$2:$H$9</definedName>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="400">
   <si>
     <t>##var</t>
   </si>
@@ -473,6 +473,18 @@
     <t>金羽仙主</t>
   </si>
   <si>
+    <t>风背余晦</t>
+  </si>
+  <si>
+    <t>炎晶狱魔</t>
+  </si>
+  <si>
+    <t>炎晶虫</t>
+  </si>
+  <si>
+    <t>炎晶狱主</t>
+  </si>
+  <si>
     <t>砺赭坂</t>
   </si>
   <si>
@@ -557,18 +569,6 @@
     <t>幽火骨煞</t>
   </si>
   <si>
-    <t>风背余晦</t>
-  </si>
-  <si>
-    <t>炎晶狱魔</t>
-  </si>
-  <si>
-    <t>炎晶虫</t>
-  </si>
-  <si>
-    <t>炎晶狱主</t>
-  </si>
-  <si>
     <t>泻砾堑</t>
   </si>
   <si>
@@ -755,6 +755,63 @@
     <t>赤幡炎将</t>
   </si>
   <si>
+    <t>雪檐古兽</t>
+  </si>
+  <si>
+    <t>残颅獠将</t>
+  </si>
+  <si>
+    <t>残骨士卒</t>
+  </si>
+  <si>
+    <t>赤纹魔狞</t>
+  </si>
+  <si>
+    <t>残骨将军</t>
+  </si>
+  <si>
+    <t>霰砾坡</t>
+  </si>
+  <si>
+    <t>链锤魔猪</t>
+  </si>
+  <si>
+    <t>蛮猪战士</t>
+  </si>
+  <si>
+    <t>蛮猪勇士</t>
+  </si>
+  <si>
+    <t>链锤野猪</t>
+  </si>
+  <si>
+    <t>融口初声</t>
+  </si>
+  <si>
+    <t>妄念猪罗</t>
+  </si>
+  <si>
+    <t>九齿天蓬</t>
+  </si>
+  <si>
+    <t>赤鬃蛮猪</t>
+  </si>
+  <si>
+    <t>凇覆苔痕</t>
+  </si>
+  <si>
+    <t>犀牛妖兵</t>
+  </si>
+  <si>
+    <t>破阵战牛</t>
+  </si>
+  <si>
+    <t>岩棘魔蜥</t>
+  </si>
+  <si>
+    <t>蛮牛魔灵</t>
+  </si>
+  <si>
     <t>寒水迟芽</t>
   </si>
   <si>
@@ -779,33 +836,6 @@
     <t>碧涛羽客</t>
   </si>
   <si>
-    <t>融口初声</t>
-  </si>
-  <si>
-    <t>妄念猪罗</t>
-  </si>
-  <si>
-    <t>九齿天蓬</t>
-  </si>
-  <si>
-    <t>赤鬃蛮猪</t>
-  </si>
-  <si>
-    <t>凇覆苔痕</t>
-  </si>
-  <si>
-    <t>犀牛妖兵</t>
-  </si>
-  <si>
-    <t>破阵战牛</t>
-  </si>
-  <si>
-    <t>岩棘魔蜥</t>
-  </si>
-  <si>
-    <t>蛮牛魔灵</t>
-  </si>
-  <si>
     <t>霁台</t>
   </si>
   <si>
@@ -818,34 +848,91 @@
     <t>玄金傀卫</t>
   </si>
   <si>
-    <t>雪檐古兽</t>
-  </si>
-  <si>
-    <t>残颅獠将</t>
-  </si>
-  <si>
-    <t>残骨士卒</t>
-  </si>
-  <si>
-    <t>赤纹魔狞</t>
-  </si>
-  <si>
-    <t>残骨将军</t>
-  </si>
-  <si>
-    <t>霰砾坡</t>
-  </si>
-  <si>
-    <t>链锤魔猪</t>
-  </si>
-  <si>
-    <t>蛮猪战士</t>
-  </si>
-  <si>
-    <t>蛮猪勇士</t>
-  </si>
-  <si>
-    <t>链锤野猪</t>
+    <t>凛冽坡</t>
+  </si>
+  <si>
+    <t>冰晶龟</t>
+  </si>
+  <si>
+    <t>寒冰巨犀</t>
+  </si>
+  <si>
+    <t>冰煞巨兽</t>
+  </si>
+  <si>
+    <t>虚浮台</t>
+  </si>
+  <si>
+    <t>冰尸妖</t>
+  </si>
+  <si>
+    <t>阴魂女煞</t>
+  </si>
+  <si>
+    <t>霜风射手</t>
+  </si>
+  <si>
+    <t>照影窗</t>
+  </si>
+  <si>
+    <t>玄冰守将</t>
+  </si>
+  <si>
+    <t>玄枢鼎君</t>
+  </si>
+  <si>
+    <t>BOSS</t>
+  </si>
+  <si>
+    <t>北境玄帝</t>
+  </si>
+  <si>
+    <t>回光藓</t>
+  </si>
+  <si>
+    <t>寒天虎</t>
+  </si>
+  <si>
+    <t>风偃枝</t>
+  </si>
+  <si>
+    <t>灵鹤</t>
+  </si>
+  <si>
+    <t>阖岫口</t>
+  </si>
+  <si>
+    <t>冰虫</t>
+  </si>
+  <si>
+    <t>墟晶魔兽</t>
+  </si>
+  <si>
+    <t>霜渊冥姬</t>
+  </si>
+  <si>
+    <t>坠尽渊</t>
+  </si>
+  <si>
+    <t>玄苍遗种</t>
+  </si>
+  <si>
+    <t>玄霜战猿</t>
+  </si>
+  <si>
+    <t>独眼魔石像</t>
+  </si>
+  <si>
+    <t>昏金岩</t>
+  </si>
+  <si>
+    <t>执旗蛮奴</t>
+  </si>
+  <si>
+    <t>浮台冥君</t>
+  </si>
+  <si>
+    <t>枷罗冥主</t>
   </si>
   <si>
     <t>版本号</t>
@@ -1080,9 +1167,6 @@
   </si>
   <si>
     <t>怪6</t>
-  </si>
-  <si>
-    <t>BOSS</t>
   </si>
   <si>
     <t>石墓顶层</t>
@@ -2515,7 +2599,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB191"/>
+  <dimension ref="A1:AB217"/>
   <sheetFormatPr defaultColWidth="8.72222222222222" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="8.81481481481481" style="12" customWidth="1"/>
@@ -5187,7 +5271,7 @@
     <row r="84" spans="2:9">
       <c r="B84" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C84,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D84,编号表!$C:$C,0))*100+E84</f>
-        <v>1019303</v>
+        <v>1026303</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>133</v>
@@ -5204,8 +5288,8 @@
       <c r="G84" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H84" s="3">
-        <v>60191086</v>
+      <c r="H84" s="12">
+        <v>60261086</v>
       </c>
       <c r="I84" s="12">
         <v>3</v>
@@ -5214,7 +5298,7 @@
     <row r="85" spans="2:9">
       <c r="B85" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C85,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D85,编号表!$C:$C,0))*100+E85</f>
-        <v>1019403</v>
+        <v>1026403</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>133</v>
@@ -5232,7 +5316,7 @@
         <v>43</v>
       </c>
       <c r="H85" s="12">
-        <v>60191087</v>
+        <v>60261087</v>
       </c>
       <c r="I85" s="12">
         <v>3</v>
@@ -5241,7 +5325,7 @@
     <row r="86" spans="2:9">
       <c r="B86" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C86,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D86,编号表!$C:$C,0))*100+E86</f>
-        <v>1019503</v>
+        <v>1026503</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>133</v>
@@ -5253,13 +5337,13 @@
         <v>3</v>
       </c>
       <c r="F86" s="18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G86" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H86" s="12">
-        <v>60191088</v>
+        <v>60261088</v>
       </c>
       <c r="I86" s="12">
         <v>3</v>
@@ -5268,52 +5352,52 @@
     <row r="87" spans="2:9">
       <c r="B87" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C87,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D87,编号表!$C:$C,0))*100+E87</f>
-        <v>1019603</v>
+        <v>1026001</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>133</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E87" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F87" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="H87" s="12">
-        <v>60191089</v>
+        <v>60264089</v>
       </c>
       <c r="I87" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="2:9">
       <c r="B88" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C88,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D88,编号表!$C:$C,0))*100+E88</f>
-        <v>1019103</v>
+        <v>1019303</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>63</v>
+        <v>137</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="E88" s="12">
         <v>3</v>
       </c>
       <c r="F88" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G88" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H88" s="12">
-        <v>60192090</v>
+      <c r="H88" s="3">
+        <v>60191090</v>
       </c>
       <c r="I88" s="12">
         <v>3</v>
@@ -5322,13 +5406,13 @@
     <row r="89" spans="2:9">
       <c r="B89" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C89,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D89,编号表!$C:$C,0))*100+E89</f>
-        <v>1020303</v>
+        <v>1019403</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E89" s="12">
         <v>3</v>
@@ -5340,7 +5424,7 @@
         <v>43</v>
       </c>
       <c r="H89" s="12">
-        <v>60201091</v>
+        <v>60191091</v>
       </c>
       <c r="I89" s="12">
         <v>3</v>
@@ -5349,13 +5433,13 @@
     <row r="90" spans="2:9">
       <c r="B90" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C90,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D90,编号表!$C:$C,0))*100+E90</f>
-        <v>1020403</v>
+        <v>1019503</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E90" s="12">
         <v>3</v>
@@ -5367,7 +5451,7 @@
         <v>43</v>
       </c>
       <c r="H90" s="12">
-        <v>60201092</v>
+        <v>60191092</v>
       </c>
       <c r="I90" s="12">
         <v>3</v>
@@ -5376,13 +5460,13 @@
     <row r="91" spans="2:9">
       <c r="B91" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C91,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D91,编号表!$C:$C,0))*100+E91</f>
-        <v>1020503</v>
+        <v>1019603</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E91" s="12">
         <v>3</v>
@@ -5394,7 +5478,7 @@
         <v>43</v>
       </c>
       <c r="H91" s="12">
-        <v>60201093</v>
+        <v>60191093</v>
       </c>
       <c r="I91" s="12">
         <v>3</v>
@@ -5403,10 +5487,10 @@
     <row r="92" spans="2:9">
       <c r="B92" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C92,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D92,编号表!$C:$C,0))*100+E92</f>
-        <v>1020103</v>
+        <v>1019103</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>63</v>
@@ -5421,7 +5505,7 @@
         <v>43</v>
       </c>
       <c r="H92" s="12">
-        <v>60202094</v>
+        <v>60192094</v>
       </c>
       <c r="I92" s="12">
         <v>3</v>
@@ -5430,40 +5514,40 @@
     <row r="93" spans="2:9">
       <c r="B93" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C93,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D93,编号表!$C:$C,0))*100+E93</f>
-        <v>1020001</v>
+        <v>1020303</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="E93" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G93" s="17" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="H93" s="12">
-        <v>60204095</v>
+        <v>60201095</v>
       </c>
       <c r="I93" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="B94" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C94,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D94,编号表!$C:$C,0))*100+E94</f>
-        <v>1021303</v>
+        <v>1020403</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E94" s="12">
         <v>3</v>
@@ -5475,7 +5559,7 @@
         <v>43</v>
       </c>
       <c r="H94" s="12">
-        <v>60211096</v>
+        <v>60201096</v>
       </c>
       <c r="I94" s="12">
         <v>3</v>
@@ -5484,13 +5568,13 @@
     <row r="95" spans="2:9">
       <c r="B95" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C95,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D95,编号表!$C:$C,0))*100+E95</f>
-        <v>1021403</v>
+        <v>1020503</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E95" s="12">
         <v>3</v>
@@ -5502,7 +5586,7 @@
         <v>43</v>
       </c>
       <c r="H95" s="12">
-        <v>60211097</v>
+        <v>60201097</v>
       </c>
       <c r="I95" s="12">
         <v>3</v>
@@ -5511,10 +5595,10 @@
     <row r="96" spans="2:9">
       <c r="B96" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C96,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D96,编号表!$C:$C,0))*100+E96</f>
-        <v>1021103</v>
+        <v>1020103</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>63</v>
@@ -5529,7 +5613,7 @@
         <v>43</v>
       </c>
       <c r="H96" s="12">
-        <v>60212098</v>
+        <v>60202098</v>
       </c>
       <c r="I96" s="12">
         <v>3</v>
@@ -5538,10 +5622,10 @@
     <row r="97" spans="2:9">
       <c r="B97" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C97,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D97,编号表!$C:$C,0))*100+E97</f>
-        <v>1021001</v>
+        <v>1020001</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D97" s="12" t="s">
         <v>80</v>
@@ -5556,7 +5640,7 @@
         <v>82</v>
       </c>
       <c r="H97" s="12">
-        <v>60214099</v>
+        <v>60204099</v>
       </c>
       <c r="I97" s="12">
         <v>1</v>
@@ -5565,7 +5649,7 @@
     <row r="98" spans="2:9">
       <c r="B98" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C98,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D98,编号表!$C:$C,0))*100+E98</f>
-        <v>1022304</v>
+        <v>1021303</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>147</v>
@@ -5574,7 +5658,7 @@
         <v>44</v>
       </c>
       <c r="E98" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F98" s="18" t="s">
         <v>148</v>
@@ -5583,16 +5667,16 @@
         <v>43</v>
       </c>
       <c r="H98" s="12">
-        <v>60221100</v>
+        <v>60211100</v>
       </c>
       <c r="I98" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C99,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D99,编号表!$C:$C,0))*100+E99</f>
-        <v>1022404</v>
+        <v>1021403</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>147</v>
@@ -5601,7 +5685,7 @@
         <v>46</v>
       </c>
       <c r="E99" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F99" s="18" t="s">
         <v>149</v>
@@ -5610,178 +5694,178 @@
         <v>43</v>
       </c>
       <c r="H99" s="12">
-        <v>60221101</v>
+        <v>60211101</v>
       </c>
       <c r="I99" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C100,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D100,编号表!$C:$C,0))*100+E100</f>
-        <v>1023304</v>
+        <v>1021103</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>44</v>
+        <v>147</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="E100" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F100" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G100" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H100" s="12">
-        <v>60231102</v>
+        <v>60212102</v>
       </c>
       <c r="I100" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C101,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D101,编号表!$C:$C,0))*100+E101</f>
-        <v>1023404</v>
+        <v>1021001</v>
       </c>
       <c r="C101" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E101" s="12">
+        <v>1</v>
+      </c>
+      <c r="F101" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D101" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E101" s="12">
-        <v>4</v>
-      </c>
-      <c r="F101" s="18" t="s">
-        <v>152</v>
-      </c>
       <c r="G101" s="17" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="H101" s="12">
-        <v>60231103</v>
+        <v>60214103</v>
       </c>
       <c r="I101" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C102,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D102,编号表!$C:$C,0))*100+E102</f>
-        <v>1024303</v>
+        <v>1022304</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D102" s="12" t="s">
         <v>44</v>
       </c>
       <c r="E102" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G102" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H102" s="12">
-        <v>60241104</v>
+        <v>60221104</v>
       </c>
       <c r="I102" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="2:9">
       <c r="B103" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C103,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D103,编号表!$C:$C,0))*100+E103</f>
-        <v>1024403</v>
+        <v>1022404</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D103" s="12" t="s">
         <v>46</v>
       </c>
       <c r="E103" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G103" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H103" s="12">
-        <v>60241105</v>
+        <v>60221105</v>
       </c>
       <c r="I103" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" spans="2:9">
       <c r="B104" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C104,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D104,编号表!$C:$C,0))*100+E104</f>
-        <v>1024503</v>
+        <v>1023304</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E104" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F104" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G104" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H104" s="12">
-        <v>60241106</v>
+        <v>60231106</v>
       </c>
       <c r="I104" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="2:9">
       <c r="B105" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C105,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D105,编号表!$C:$C,0))*100+E105</f>
-        <v>1024103</v>
+        <v>1023404</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>63</v>
+        <v>154</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="E105" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F105" s="18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G105" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H105" s="12">
-        <v>60242107</v>
+        <v>60231107</v>
       </c>
       <c r="I105" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="2:9">
       <c r="B106" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C106,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D106,编号表!$C:$C,0))*100+E106</f>
-        <v>1025303</v>
+        <v>1024303</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>157</v>
@@ -5799,7 +5883,7 @@
         <v>43</v>
       </c>
       <c r="H106" s="12">
-        <v>60251108</v>
+        <v>60241108</v>
       </c>
       <c r="I106" s="12">
         <v>3</v>
@@ -5808,7 +5892,7 @@
     <row r="107" spans="2:9">
       <c r="B107" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C107,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D107,编号表!$C:$C,0))*100+E107</f>
-        <v>1025403</v>
+        <v>1024403</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>157</v>
@@ -5826,7 +5910,7 @@
         <v>43</v>
       </c>
       <c r="H107" s="12">
-        <v>60251109</v>
+        <v>60241109</v>
       </c>
       <c r="I107" s="12">
         <v>3</v>
@@ -5835,25 +5919,25 @@
     <row r="108" spans="2:9">
       <c r="B108" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C108,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D108,编号表!$C:$C,0))*100+E108</f>
-        <v>1025103</v>
+        <v>1024503</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D108" s="8" t="s">
-        <v>63</v>
+      <c r="D108" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="E108" s="12">
         <v>3</v>
       </c>
       <c r="F108" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G108" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H108" s="12">
-        <v>60252110</v>
+        <v>60241110</v>
       </c>
       <c r="I108" s="12">
         <v>3</v>
@@ -5862,34 +5946,34 @@
     <row r="109" spans="2:9">
       <c r="B109" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C109,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D109,编号表!$C:$C,0))*100+E109</f>
-        <v>1025001</v>
+        <v>1024103</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D109" s="12" t="s">
-        <v>80</v>
+      <c r="D109" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="E109" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="H109" s="12">
-        <v>60254111</v>
+        <v>60242111</v>
       </c>
       <c r="I109" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="2:9">
       <c r="B110" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C110,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D110,编号表!$C:$C,0))*100+E110</f>
-        <v>1026303</v>
+        <v>1025303</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>161</v>
@@ -5907,7 +5991,7 @@
         <v>43</v>
       </c>
       <c r="H110" s="12">
-        <v>60261112</v>
+        <v>60251112</v>
       </c>
       <c r="I110" s="12">
         <v>3</v>
@@ -5916,7 +6000,7 @@
     <row r="111" spans="2:9">
       <c r="B111" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C111,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D111,编号表!$C:$C,0))*100+E111</f>
-        <v>1026403</v>
+        <v>1025403</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>161</v>
@@ -5934,7 +6018,7 @@
         <v>43</v>
       </c>
       <c r="H111" s="12">
-        <v>60261113</v>
+        <v>60251113</v>
       </c>
       <c r="I111" s="12">
         <v>3</v>
@@ -5943,25 +6027,25 @@
     <row r="112" spans="2:9">
       <c r="B112" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C112,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D112,编号表!$C:$C,0))*100+E112</f>
-        <v>1026503</v>
+        <v>1025103</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="12" t="s">
-        <v>48</v>
+      <c r="D112" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="E112" s="12">
         <v>3</v>
       </c>
       <c r="F112" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G112" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H112" s="12">
-        <v>60261114</v>
+        <v>60252114</v>
       </c>
       <c r="I112" s="12">
         <v>3</v>
@@ -5970,7 +6054,7 @@
     <row r="113" spans="2:9">
       <c r="B113" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C113,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D113,编号表!$C:$C,0))*100+E113</f>
-        <v>1026001</v>
+        <v>1025001</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>161</v>
@@ -5988,7 +6072,7 @@
         <v>82</v>
       </c>
       <c r="H113" s="12">
-        <v>60264115</v>
+        <v>60254115</v>
       </c>
       <c r="I113" s="12">
         <v>1</v>
@@ -7239,34 +7323,34 @@
     <row r="160" spans="2:9">
       <c r="B160" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C160,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D160,编号表!$C:$C,0))*100+E160</f>
-        <v>1059103</v>
+        <v>1064001</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>227</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E160" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F160" s="18" t="s">
         <v>228</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="H160" s="12">
-        <v>60592164</v>
+        <v>60644163</v>
       </c>
       <c r="I160" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="161" spans="2:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="2:27">
       <c r="B161" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C161,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D161,编号表!$C:$C,0))*100+E161</f>
-        <v>1059304</v>
+        <v>1064304</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>227</v>
@@ -7284,43 +7368,61 @@
         <v>43</v>
       </c>
       <c r="H161" s="12">
-        <v>60591162</v>
+        <v>60641162</v>
       </c>
       <c r="I161" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="2:9">
+    <row r="162" ht="14.4" spans="2:27">
       <c r="B162" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C162,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D162,编号表!$C:$C,0))*100+E162</f>
-        <v>1059404</v>
+        <v>1064103</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>227</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E162" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F162" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G162" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H162" s="12">
-        <v>60591163</v>
+        <v>60642164</v>
       </c>
       <c r="I162" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="163" spans="2:9">
+        <v>3</v>
+      </c>
+      <c r="J162"/>
+      <c r="K162"/>
+      <c r="L162"/>
+      <c r="M162"/>
+      <c r="N162"/>
+      <c r="O162"/>
+      <c r="P162"/>
+      <c r="Q162"/>
+      <c r="R162"/>
+      <c r="S162"/>
+      <c r="T162"/>
+      <c r="U162"/>
+      <c r="V162"/>
+      <c r="W162"/>
+      <c r="X162"/>
+      <c r="Y162"/>
+      <c r="Z162"/>
+      <c r="AA162"/>
+    </row>
+    <row r="163" spans="2:27">
       <c r="B163" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C163,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D163,编号表!$C:$C,0))*100+E163</f>
-        <v>1059503</v>
+        <v>1064504</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>227</v>
@@ -7329,25 +7431,25 @@
         <v>48</v>
       </c>
       <c r="E163" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F163" s="18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G163" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H163" s="12">
-        <v>60591165</v>
+        <v>60641165</v>
       </c>
       <c r="I163" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="164" spans="2:9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="2:27">
       <c r="B164" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C164,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D164,编号表!$C:$C,0))*100+E164</f>
-        <v>1059604</v>
+        <v>1064604</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>227</v>
@@ -7359,25 +7461,25 @@
         <v>4</v>
       </c>
       <c r="F164" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G164" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H164" s="12">
-        <v>60591166</v>
+        <v>60641166</v>
       </c>
       <c r="I164" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="2:9">
+    <row r="165" spans="2:27">
       <c r="B165" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C165,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D165,编号表!$C:$C,0))*100+E165</f>
-        <v>1060103</v>
+        <v>1065103</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D165" s="12" t="s">
         <v>63</v>
@@ -7386,31 +7488,31 @@
         <v>3</v>
       </c>
       <c r="F165" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G165" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H165" s="12">
-        <v>60602169</v>
+        <v>60652167</v>
       </c>
       <c r="I165" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="2:9">
+    <row r="166" spans="2:27">
       <c r="B166" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C166,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D166,编号表!$C:$C,0))*100+E166</f>
-        <v>1060304</v>
+        <v>1065303</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D166" s="12" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F166" s="18" t="s">
         <v>233</v>
@@ -7419,19 +7521,19 @@
         <v>43</v>
       </c>
       <c r="H166" s="12">
-        <v>60601167</v>
+        <v>60651168</v>
       </c>
       <c r="I166" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="167" spans="2:9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="2:27">
       <c r="B167" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C167,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D167,编号表!$C:$C,0))*100+E167</f>
-        <v>1060404</v>
+        <v>1065404</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D167" s="12" t="s">
         <v>46</v>
@@ -7446,19 +7548,19 @@
         <v>43</v>
       </c>
       <c r="H167" s="12">
-        <v>60601168</v>
+        <v>60651169</v>
       </c>
       <c r="I167" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="2:9">
+    <row r="168" spans="2:27">
       <c r="B168" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C168,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D168,编号表!$C:$C,0))*100+E168</f>
-        <v>1060504</v>
+        <v>1065504</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D168" s="12" t="s">
         <v>48</v>
@@ -7467,31 +7569,31 @@
         <v>4</v>
       </c>
       <c r="F168" s="18" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G168" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H168" s="12">
-        <v>60601170</v>
+        <v>60651170</v>
       </c>
       <c r="I168" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="2:9">
+    <row r="169" spans="2:27">
       <c r="B169" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C169,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D169,编号表!$C:$C,0))*100+E169</f>
-        <v>1061103</v>
+        <v>1065604</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E169" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" s="18" t="s">
         <v>236</v>
@@ -7500,184 +7602,202 @@
         <v>43</v>
       </c>
       <c r="H169" s="12">
-        <v>60612173</v>
+        <v>60651171</v>
       </c>
       <c r="I169" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="170" spans="2:9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="2:27">
       <c r="B170" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C170,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D170,编号表!$C:$C,0))*100+E170</f>
-        <v>1061001</v>
+        <v>1061103</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E170" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F170" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G170" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H170" s="12">
-        <v>60611171</v>
+        <v>60612174</v>
       </c>
       <c r="I170" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="2:9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" ht="14.4" spans="2:27">
       <c r="B171" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C171,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D171,编号表!$C:$C,0))*100+E171</f>
-        <v>1061404</v>
+        <v>1061001</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E171" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F171" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G171" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H171" s="12">
-        <v>60611172</v>
+        <v>60614172</v>
       </c>
       <c r="I171" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="172" spans="2:9">
+        <v>1</v>
+      </c>
+      <c r="J171"/>
+      <c r="K171"/>
+      <c r="L171"/>
+      <c r="M171"/>
+      <c r="N171"/>
+      <c r="O171"/>
+      <c r="P171"/>
+      <c r="Q171"/>
+      <c r="R171"/>
+      <c r="S171"/>
+      <c r="T171"/>
+      <c r="U171"/>
+      <c r="V171"/>
+      <c r="W171"/>
+      <c r="X171"/>
+      <c r="Y171"/>
+      <c r="Z171"/>
+      <c r="AA171"/>
+    </row>
+    <row r="172" spans="2:27">
       <c r="B172" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C172,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D172,编号表!$C:$C,0))*100+E172</f>
-        <v>1061504</v>
+        <v>1061404</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E172" s="12">
         <v>4</v>
       </c>
       <c r="F172" s="18" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G172" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H172" s="12">
-        <v>60611174</v>
+        <v>60611173</v>
       </c>
       <c r="I172" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="2:9">
+    <row r="173" spans="2:27">
       <c r="B173" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C173,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D173,编号表!$C:$C,0))*100+E173</f>
-        <v>1062101</v>
+        <v>1061504</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E173" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F173" s="18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G173" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H173" s="12">
-        <v>60622176</v>
+        <v>60611175</v>
       </c>
       <c r="I173" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="2:9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="2:27">
       <c r="B174" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C174,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D174,编号表!$C:$C,0))*100+E174</f>
-        <v>1062304</v>
+        <v>1062101</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E174" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F174" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G174" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H174" s="12">
-        <v>60621175</v>
+        <v>60622177</v>
       </c>
       <c r="I174" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="175" spans="2:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="2:27">
       <c r="B175" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C175,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D175,编号表!$C:$C,0))*100+E175</f>
-        <v>1062404</v>
+        <v>1062304</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D175" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E175" s="12">
         <v>4</v>
       </c>
       <c r="F175" s="18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G175" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H175" s="12">
-        <v>60621177</v>
+        <v>60621176</v>
       </c>
       <c r="I175" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="2:9">
+    <row r="176" spans="2:27">
       <c r="B176" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C176,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D176,编号表!$C:$C,0))*100+E176</f>
-        <v>1062504</v>
+        <v>1062404</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E176" s="12">
         <v>4</v>
@@ -7695,22 +7815,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="2:9">
+    <row r="177" spans="1:9">
       <c r="B177" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C177,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D177,编号表!$C:$C,0))*100+E177</f>
-        <v>1062604</v>
+        <v>1062504</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E177" s="12">
         <v>4</v>
       </c>
       <c r="F177" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G177" s="17" t="s">
         <v>43</v>
@@ -7722,19 +7842,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="2:9">
+    <row r="178" spans="1:9">
       <c r="B178" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C178,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D178,编号表!$C:$C,0))*100+E178</f>
-        <v>1063103</v>
+        <v>1062604</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E178" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F178" s="18" t="s">
         <v>245</v>
@@ -7743,154 +7863,154 @@
         <v>43</v>
       </c>
       <c r="H178" s="12">
-        <v>60632181</v>
+        <v>60621180</v>
       </c>
       <c r="I178" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="179" spans="2:9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="B179" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C179,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D179,编号表!$C:$C,0))*100+E179</f>
-        <v>1063304</v>
+        <v>1059103</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E179" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F179" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G179" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H179" s="12">
-        <v>60631180</v>
+        <v>60592183</v>
       </c>
       <c r="I179" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="180" spans="2:9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="B180" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C180,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D180,编号表!$C:$C,0))*100+E180</f>
-        <v>1063404</v>
+        <v>1059304</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E180" s="12">
         <v>4</v>
       </c>
       <c r="F180" s="18" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G180" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H180" s="12">
-        <v>60631182</v>
+        <v>60591181</v>
       </c>
       <c r="I180" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="2:9">
+    <row r="181" spans="1:9">
       <c r="B181" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C181,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D181,编号表!$C:$C,0))*100+E181</f>
-        <v>1063504</v>
+        <v>1059404</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E181" s="12">
         <v>4</v>
       </c>
       <c r="F181" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G181" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H181" s="12">
-        <v>60631183</v>
+        <v>60591182</v>
       </c>
       <c r="I181" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="2:9">
+    <row r="182" spans="1:9">
       <c r="B182" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C182,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D182,编号表!$C:$C,0))*100+E182</f>
-        <v>1064001</v>
+        <v>1059503</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="E182" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F182" s="18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G182" s="17" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="H182" s="12">
-        <v>60644185</v>
+        <v>60591184</v>
       </c>
       <c r="I182" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="2:9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="B183" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C183,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D183,编号表!$C:$C,0))*100+E183</f>
-        <v>1064304</v>
+        <v>1059604</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E183" s="12">
         <v>4</v>
       </c>
       <c r="F183" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G183" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H183" s="12">
-        <v>60641184</v>
+        <v>60591185</v>
       </c>
       <c r="I183" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="2:9">
+    <row r="184" spans="1:9">
       <c r="B184" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C184,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D184,编号表!$C:$C,0))*100+E184</f>
-        <v>1064103</v>
+        <v>1060103</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D184" s="12" t="s">
         <v>63</v>
@@ -7905,184 +8025,185 @@
         <v>43</v>
       </c>
       <c r="H184" s="12">
-        <v>60641186</v>
+        <v>60602188</v>
       </c>
       <c r="I184" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="2:9">
+    <row r="185" spans="1:9">
       <c r="B185" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C185,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D185,编号表!$C:$C,0))*100+E185</f>
-        <v>1064504</v>
+        <v>1060304</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D185" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E185" s="12">
         <v>4</v>
       </c>
       <c r="F185" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G185" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H185" s="12">
-        <v>60641187</v>
+        <v>60601186</v>
       </c>
       <c r="I185" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="2:9">
+    <row r="186" spans="1:9">
+      <c r="A186" s="8"/>
       <c r="B186" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C186,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D186,编号表!$C:$C,0))*100+E186</f>
-        <v>1064604</v>
+        <v>1060404</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D186" s="12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E186" s="12">
         <v>4</v>
       </c>
       <c r="F186" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G186" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H186" s="12">
-        <v>60641188</v>
+        <v>60601187</v>
       </c>
       <c r="I186" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="2:9">
+    <row r="187" spans="1:9">
       <c r="B187" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C187,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D187,编号表!$C:$C,0))*100+E187</f>
-        <v>1065103</v>
+        <v>1060504</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D187" s="12" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E187" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F187" s="18" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G187" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H187" s="12">
-        <v>60652189</v>
+        <v>60601189</v>
       </c>
       <c r="I187" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188" spans="2:9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="B188" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C188,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D188,编号表!$C:$C,0))*100+E188</f>
-        <v>1065303</v>
+        <v>1063103</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D188" s="12" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E188" s="12">
         <v>3</v>
       </c>
       <c r="F188" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G188" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H188" s="12">
-        <v>60651190</v>
+        <v>60632191</v>
       </c>
       <c r="I188" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="2:9">
+    <row r="189" spans="1:9">
       <c r="B189" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C189,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D189,编号表!$C:$C,0))*100+E189</f>
-        <v>1065404</v>
+        <v>1063304</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D189" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E189" s="12">
         <v>4</v>
       </c>
       <c r="F189" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G189" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H189" s="12">
-        <v>60651191</v>
+        <v>60631190</v>
       </c>
       <c r="I189" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="2:9">
+    <row r="190" spans="1:9">
       <c r="B190" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C190,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D190,编号表!$C:$C,0))*100+E190</f>
-        <v>1065504</v>
+        <v>1063404</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D190" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E190" s="12">
         <v>4</v>
       </c>
       <c r="F190" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G190" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H190" s="12">
-        <v>60651192</v>
+        <v>60631192</v>
       </c>
       <c r="I190" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="2:9">
+    <row r="191" spans="1:9">
       <c r="B191" s="12">
         <f>1000000+INDEX(编号表!$B:$B,MATCH(C191,编号表!$A:$A,0))*1000+INDEX(编号表!$D:$D,MATCH(D191,编号表!$C:$C,0))*100+E191</f>
-        <v>1065604</v>
+        <v>1063504</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D191" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E191" s="12">
         <v>4</v>
@@ -8094,14 +8215,690 @@
         <v>43</v>
       </c>
       <c r="H191" s="12">
-        <v>60651193</v>
+        <v>60631193</v>
       </c>
       <c r="I191" s="12">
         <v>4</v>
       </c>
     </row>
+    <row r="192" spans="1:9">
+      <c r="B192" s="12">
+        <v>1066304</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E192" s="12">
+        <v>4</v>
+      </c>
+      <c r="F192" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="G192" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H192" s="12">
+        <v>60661194</v>
+      </c>
+      <c r="I192" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9">
+      <c r="B193" s="12">
+        <v>1066404</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D193" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E193" s="12">
+        <v>4</v>
+      </c>
+      <c r="F193" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="G193" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H193" s="12">
+        <v>60661195</v>
+      </c>
+      <c r="I193" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9">
+      <c r="B194" s="12">
+        <v>1066504</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E194" s="12">
+        <v>4</v>
+      </c>
+      <c r="F194" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="G194" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H194" s="12">
+        <v>60661196</v>
+      </c>
+      <c r="I194" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9">
+      <c r="B195" s="12">
+        <v>1066103</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D195" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E195" s="12">
+        <v>3</v>
+      </c>
+      <c r="F195" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="G195" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H195" s="12">
+        <v>60662197</v>
+      </c>
+      <c r="I195" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9">
+      <c r="B196" s="12">
+        <v>1067304</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E196" s="12">
+        <v>4</v>
+      </c>
+      <c r="F196" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="G196" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H196" s="12">
+        <v>60671198</v>
+      </c>
+      <c r="I196" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9">
+      <c r="B197" s="12">
+        <v>1067404</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E197" s="12">
+        <v>4</v>
+      </c>
+      <c r="F197" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="G197" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H197" s="12">
+        <v>60671199</v>
+      </c>
+      <c r="I197" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9">
+      <c r="B198" s="12">
+        <v>1067504</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E198" s="12">
+        <v>4</v>
+      </c>
+      <c r="F198" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="G198" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H198" s="12">
+        <v>60671200</v>
+      </c>
+      <c r="I198" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9">
+      <c r="B199" s="12">
+        <v>1067103</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E199" s="12">
+        <v>3</v>
+      </c>
+      <c r="F199" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="G199" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H199" s="12">
+        <v>60672201</v>
+      </c>
+      <c r="I199" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9">
+      <c r="B200" s="12">
+        <v>1068404</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D200" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E200" s="12">
+        <v>4</v>
+      </c>
+      <c r="F200" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="G200" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H200" s="12">
+        <v>60681203</v>
+      </c>
+      <c r="I200" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9">
+      <c r="B201" s="12">
+        <v>1068504</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D201" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E201" s="12">
+        <v>4</v>
+      </c>
+      <c r="F201" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="G201" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H201" s="12">
+        <v>60681204</v>
+      </c>
+      <c r="I201" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9">
+      <c r="B202" s="12">
+        <v>1068103</v>
+      </c>
+      <c r="C202" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D202" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E202" s="12">
+        <v>3</v>
+      </c>
+      <c r="F202" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="G202" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H202" s="12">
+        <v>60682205</v>
+      </c>
+      <c r="I202" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9">
+      <c r="B203" s="12">
+        <v>1068001</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E203" s="12">
+        <v>1</v>
+      </c>
+      <c r="F203" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="G203" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H203" s="12">
+        <v>60684206</v>
+      </c>
+      <c r="I203" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9">
+      <c r="B204" s="12">
+        <v>1069304</v>
+      </c>
+      <c r="C204" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E204" s="12">
+        <v>4</v>
+      </c>
+      <c r="F204" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="G204" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H204" s="12">
+        <v>60691207</v>
+      </c>
+      <c r="I204" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9">
+      <c r="B205" s="12">
+        <v>1070304</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D205" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E205" s="12">
+        <v>4</v>
+      </c>
+      <c r="F205" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="G205" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H205" s="12">
+        <v>60701208</v>
+      </c>
+      <c r="I205" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9">
+      <c r="B206" s="12">
+        <v>1071304</v>
+      </c>
+      <c r="C206" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E206" s="12">
+        <v>4</v>
+      </c>
+      <c r="F206" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="G206" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H206" s="12">
+        <v>60711209</v>
+      </c>
+      <c r="I206" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="2:9">
+      <c r="B207" s="12">
+        <v>1071504</v>
+      </c>
+      <c r="C207" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E207" s="12">
+        <v>4</v>
+      </c>
+      <c r="F207" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="G207" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H207" s="12">
+        <v>60711211</v>
+      </c>
+      <c r="I207" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="2:9">
+      <c r="B208" s="12">
+        <v>1071103</v>
+      </c>
+      <c r="C208" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D208" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E208" s="12">
+        <v>3</v>
+      </c>
+      <c r="F208" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="G208" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H208" s="12">
+        <v>60712212</v>
+      </c>
+      <c r="I208" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9">
+      <c r="B209" s="12">
+        <v>1071001</v>
+      </c>
+      <c r="C209" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E209" s="12">
+        <v>1</v>
+      </c>
+      <c r="F209" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="G209" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H209" s="12">
+        <v>60714213</v>
+      </c>
+      <c r="I209" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="2:9">
+      <c r="B210" s="12">
+        <v>1072304</v>
+      </c>
+      <c r="C210" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E210" s="12">
+        <v>4</v>
+      </c>
+      <c r="F210" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="G210" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H210" s="12">
+        <v>60721214</v>
+      </c>
+      <c r="I210" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9">
+      <c r="B211" s="12">
+        <v>1072404</v>
+      </c>
+      <c r="C211" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E211" s="12">
+        <v>4</v>
+      </c>
+      <c r="F211" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G211" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H211" s="12">
+        <v>60721215</v>
+      </c>
+      <c r="I211" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="2:9">
+      <c r="B212" s="12">
+        <v>1072504</v>
+      </c>
+      <c r="C212" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E212" s="12">
+        <v>4</v>
+      </c>
+      <c r="F212" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G212" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H212" s="12">
+        <v>60721216</v>
+      </c>
+      <c r="I212" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9">
+      <c r="B213" s="12">
+        <v>1072103</v>
+      </c>
+      <c r="C213" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E213" s="12">
+        <v>3</v>
+      </c>
+      <c r="F213" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="G213" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H213" s="12">
+        <v>60722217</v>
+      </c>
+      <c r="I213" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9">
+      <c r="B214" s="12">
+        <v>1073404</v>
+      </c>
+      <c r="C214" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E214" s="12">
+        <v>4</v>
+      </c>
+      <c r="F214" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="G214" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H214" s="12">
+        <v>60731219</v>
+      </c>
+      <c r="I214" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="2:9">
+      <c r="B215" s="12">
+        <v>1073504</v>
+      </c>
+      <c r="C215" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E215" s="12">
+        <v>4</v>
+      </c>
+      <c r="F215" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="G215" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H215" s="12">
+        <v>60731220</v>
+      </c>
+      <c r="I215" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="2:9">
+      <c r="B216" s="12">
+        <v>1073103</v>
+      </c>
+      <c r="C216" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E216" s="12">
+        <v>3</v>
+      </c>
+      <c r="F216" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="G216" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H216" s="12">
+        <v>60732221</v>
+      </c>
+      <c r="I216" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="2:9">
+      <c r="B217" s="12">
+        <v>1073001</v>
+      </c>
+      <c r="C217" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E217" s="12">
+        <v>1</v>
+      </c>
+      <c r="F217" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="G217" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H217" s="12">
+        <v>60734222</v>
+      </c>
+      <c r="I217" s="12">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:Z191" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:AB217" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="2">
@@ -8154,133 +8951,133 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="B1" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="B6" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -8386,64 +9183,64 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -8451,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>43</v>
@@ -8522,7 +9319,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>43</v>
@@ -8563,7 +9360,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>43</v>
@@ -8586,7 +9383,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>43</v>
@@ -8627,7 +9424,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>43</v>
@@ -8674,7 +9471,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>82</v>
@@ -8691,7 +9488,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>43</v>
@@ -8738,7 +9535,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>43</v>
@@ -8779,7 +9576,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>43</v>
@@ -8820,7 +9617,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>82</v>
@@ -8837,7 +9634,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>43</v>
@@ -8890,7 +9687,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>43</v>
@@ -8907,7 +9704,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>43</v>
@@ -8948,7 +9745,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>43</v>
@@ -8983,7 +9780,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>43</v>
@@ -9024,7 +9821,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>82</v>
@@ -9041,7 +9838,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>43</v>
@@ -9076,7 +9873,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>82</v>
@@ -9093,7 +9890,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>43</v>
@@ -9128,7 +9925,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>43</v>
@@ -9163,7 +9960,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>43</v>
@@ -9198,7 +9995,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>82</v>
@@ -9215,7 +10012,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>43</v>
@@ -9250,7 +10047,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>43</v>
@@ -9297,7 +10094,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>43</v>
@@ -9344,7 +10141,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>43</v>
@@ -9379,7 +10176,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>82</v>
@@ -9396,7 +10193,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>43</v>
@@ -9425,7 +10222,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>82</v>
@@ -9442,7 +10239,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>82</v>
@@ -9459,7 +10256,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>82</v>
@@ -9476,10 +10273,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="F38">
         <v>1000000</v>
@@ -9490,10 +10287,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:6">
@@ -9501,10 +10298,10 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" spans="1:6">
@@ -9512,10 +10309,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" spans="1:6">
@@ -9523,10 +10320,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" spans="1:6">
@@ -9534,10 +10331,10 @@
         <v>6</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:6">
@@ -9545,7 +10342,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>63</v>
@@ -9556,10 +10353,10 @@
         <v>8</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>336</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:6">
@@ -9567,7 +10364,7 @@
         <v>9</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:6">
@@ -9575,7 +10372,7 @@
         <v>10</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:6">
@@ -9583,7 +10380,7 @@
         <v>11</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1" spans="1:2">
@@ -9591,7 +10388,7 @@
         <v>12</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:2">
@@ -9599,7 +10396,7 @@
         <v>13</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:2">
@@ -9607,7 +10404,7 @@
         <v>14</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" spans="1:2">
@@ -9615,7 +10412,7 @@
         <v>15</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" spans="1:2">
@@ -9623,7 +10420,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" spans="1:2">
@@ -9631,7 +10428,7 @@
         <v>17</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1" spans="1:2">
@@ -9639,7 +10436,7 @@
         <v>18</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1" spans="1:2">
@@ -9647,7 +10444,7 @@
         <v>19</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1" spans="1:2">
@@ -9655,7 +10452,7 @@
         <v>20</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1" spans="1:2">
@@ -9663,7 +10460,7 @@
         <v>21</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1" spans="1:2">
@@ -9671,7 +10468,7 @@
         <v>22</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1" spans="1:2">
@@ -9679,7 +10476,7 @@
         <v>23</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1" spans="1:2">
@@ -9687,7 +10484,7 @@
         <v>24</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1" spans="1:2">
@@ -9695,7 +10492,7 @@
         <v>25</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1" spans="1:2">
@@ -9703,7 +10500,7 @@
         <v>26</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1" spans="1:2">
@@ -9711,7 +10508,7 @@
         <v>27</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1" spans="1:2">
@@ -9719,7 +10516,7 @@
         <v>28</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1" spans="1:2">
@@ -9727,7 +10524,7 @@
         <v>29</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1" spans="1:2">
@@ -9735,7 +10532,7 @@
         <v>30</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1" spans="1:2">
@@ -9743,7 +10540,7 @@
         <v>31</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1" spans="1:2">
@@ -9751,7 +10548,7 @@
         <v>32</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1" spans="1:2">
@@ -9759,7 +10556,7 @@
         <v>33</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1" spans="1:2">
@@ -9767,7 +10564,7 @@
         <v>34</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1" spans="1:2">
@@ -9775,7 +10572,7 @@
         <v>35</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1" spans="1:2">
@@ -9783,7 +10580,7 @@
         <v>36</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1" spans="1:2">
@@ -9791,7 +10588,7 @@
         <v>37</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1" spans="1:2">
@@ -9799,7 +10596,7 @@
         <v>38</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:2">
@@ -9807,7 +10604,7 @@
         <v>39</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1" spans="1:2">
@@ -9815,7 +10612,7 @@
         <v>40</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -9904,13 +10701,13 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>13</v>
@@ -9924,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>336</v>
+        <v>269</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -9946,7 +10743,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -9976,7 +10773,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="H5" s="3"/>
     </row>
@@ -9994,10 +10791,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
@@ -10014,10 +10811,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
@@ -10034,7 +10831,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
@@ -10051,7 +10848,7 @@
         <v>7</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
@@ -10068,10 +10865,10 @@
         <v>8</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
@@ -10088,10 +10885,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
@@ -10104,7 +10901,7 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:8">
@@ -10175,7 +10972,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -10183,7 +10980,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:4">
       <c r="A21" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -10191,7 +10988,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1" spans="1:4">
       <c r="A22" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -10199,7 +10996,7 @@
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:4">
       <c r="A23" s="8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -10207,7 +11004,7 @@
     </row>
     <row r="24" ht="14.25" customHeight="1" spans="1:4">
       <c r="A24" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -10215,7 +11012,7 @@
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -10223,7 +11020,7 @@
     </row>
     <row r="26" ht="14.25" customHeight="1" spans="1:4">
       <c r="A26" s="8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -10231,7 +11028,7 @@
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:4">
       <c r="A27" s="8" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -10239,7 +11036,7 @@
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -10247,7 +11044,7 @@
     </row>
     <row r="29" ht="14.25" customHeight="1" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -10255,7 +11052,7 @@
     </row>
     <row r="30" ht="14.25" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -10263,7 +11060,7 @@
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -10271,7 +11068,7 @@
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -10279,7 +11076,7 @@
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="B33">
         <v>32</v>
@@ -10287,7 +11084,7 @@
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B34">
         <v>33</v>
@@ -10295,7 +11092,7 @@
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:2">
       <c r="A35" s="3" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -10303,7 +11100,7 @@
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:2">
       <c r="A36" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -10311,7 +11108,7 @@
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:2">
       <c r="A37" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="B37">
         <v>36</v>
@@ -10319,7 +11116,7 @@
     </row>
     <row r="38" ht="14.25" customHeight="1" spans="1:2">
       <c r="A38" s="3" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="B38">
         <v>37</v>
@@ -10327,7 +11124,7 @@
     </row>
     <row r="39" ht="14.25" customHeight="1" spans="1:2">
       <c r="A39" s="3" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="B39">
         <v>38</v>
@@ -10335,7 +11132,7 @@
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="B40">
         <v>39</v>
@@ -10343,7 +11140,7 @@
     </row>
     <row r="41" ht="14.25" customHeight="1" spans="1:2">
       <c r="A41" s="3" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -10351,7 +11148,7 @@
     </row>
     <row r="42" ht="14.25" customHeight="1" spans="1:2">
       <c r="A42" s="3" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="B42">
         <v>41</v>
@@ -10423,7 +11220,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -10495,7 +11292,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="B60">
         <v>59</v>
@@ -10503,7 +11300,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="B61">
         <v>60</v>
@@ -10511,7 +11308,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B62">
         <v>61</v>
@@ -10519,7 +11316,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B63">
         <v>62</v>
@@ -10527,7 +11324,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B64">
         <v>63</v>
@@ -10535,7 +11332,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="B65">
         <v>64</v>
@@ -10543,7 +11340,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="B66">
         <v>65</v>
